--- a/datasets/tax_dataset.xlsx
+++ b/datasets/tax_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G181"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4965,6 +4965,281 @@
         <v>0</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>T_DB_1</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2500</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>T_DB_2</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>T_DB_3</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>T_DB_4</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1</v>
+      </c>
+      <c r="G185" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>T_DB_5</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1</v>
+      </c>
+      <c r="G186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>T_DB_6</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>0</v>
+      </c>
+      <c r="C187" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="n">
+        <v>6</v>
+      </c>
+      <c r="G187" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>T_DB_7</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>6</v>
+      </c>
+      <c r="G188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>T_DB_8</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
+      <c r="C189" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="n">
+        <v>6</v>
+      </c>
+      <c r="G189" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>T_DB_9</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>0</v>
+      </c>
+      <c r="C190" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="n">
+        <v>6</v>
+      </c>
+      <c r="G190" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>T_DB_10</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="n">
+        <v>6</v>
+      </c>
+      <c r="G191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>T_DB_11</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>0</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>6</v>
+      </c>
+      <c r="G192" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/datasets/tax_dataset.xlsx
+++ b/datasets/tax_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4968,67 +4968,67 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>T_DB_1</t>
+          <t>T_SEED_181</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>2500</v>
+        <v>624.4</v>
       </c>
       <c r="D182" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>T_DB_2</t>
+          <t>T_SEED_182</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>1800</v>
+        <v>5794.4</v>
       </c>
       <c r="D183" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>T_DB_3</t>
+          <t>T_SEED_183</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C184" t="n">
-        <v>5000</v>
+        <v>6156.16</v>
       </c>
       <c r="D184" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E184" t="n">
         <v>1</v>
@@ -5043,201 +5043,426 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>T_DB_4</t>
+          <t>T_SEED_184</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>2200</v>
+        <v>3819.18</v>
       </c>
       <c r="D185" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>T_DB_5</t>
+          <t>T_SEED_185</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186" t="n">
-        <v>4500</v>
+        <v>5865.99</v>
       </c>
       <c r="D186" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E186" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>T_DB_6</t>
+          <t>T_SEED_186</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>2100</v>
+        <v>5577.33</v>
       </c>
       <c r="D187" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>T_DB_7</t>
+          <t>T_SEED_187</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>2100</v>
+        <v>2228.32</v>
       </c>
       <c r="D188" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="F188" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>T_DB_8</t>
+          <t>T_SEED_188</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>2100</v>
+        <v>9025.59</v>
       </c>
       <c r="D189" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>T_DB_9</t>
+          <t>T_SEED_189</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>2100</v>
+        <v>7301.74</v>
       </c>
       <c r="D190" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>T_DB_10</t>
+          <t>T_SEED_190</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>2100</v>
+        <v>2363.07</v>
       </c>
       <c r="D191" t="n">
         <v>2026</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>T_DB_11</t>
+          <t>T_SEED_191</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>2100</v>
+        <v>2196.17</v>
       </c>
       <c r="D192" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F192" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>T_SEED_192</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="n">
+        <v>9892.92</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>T_SEED_193</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2447.35</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>T_SEED_194</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>0</v>
+      </c>
+      <c r="C195" t="n">
+        <v>7491.09</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>T_SEED_195</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
+      <c r="C196" t="n">
+        <v>4503.53</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>T_SEED_196</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
+      <c r="C197" t="n">
+        <v>8338.52</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>T_SEED_197</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>0</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4389.41</v>
+      </c>
+      <c r="D198" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E198" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F198" t="n">
+        <v>0</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>T_SEED_198</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>0</v>
+      </c>
+      <c r="C199" t="n">
+        <v>9758.200000000001</v>
+      </c>
+      <c r="D199" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>T_SEED_199</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="n">
+        <v>8098.62</v>
+      </c>
+      <c r="D200" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" t="n">
+        <v>0</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>T_SEED_200</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
+      <c r="C201" t="n">
+        <v>7139.04</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/tax_dataset.xlsx
+++ b/datasets/tax_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4968,67 +4968,67 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>T_SEED_181</t>
+          <t>T_DB_1</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>0</v>
       </c>
       <c r="C182" t="n">
-        <v>624.4</v>
+        <v>2500</v>
       </c>
       <c r="D182" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>T_SEED_182</t>
+          <t>T_DB_2</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>0</v>
       </c>
       <c r="C183" t="n">
-        <v>5794.4</v>
+        <v>1800</v>
       </c>
       <c r="D183" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>T_SEED_183</t>
+          <t>T_DB_3</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C184" t="n">
-        <v>6156.16</v>
+        <v>5000</v>
       </c>
       <c r="D184" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E184" t="n">
         <v>1</v>
@@ -5043,426 +5043,201 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>T_SEED_184</t>
+          <t>T_DB_4</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C185" t="n">
-        <v>3819.18</v>
+        <v>2200</v>
       </c>
       <c r="D185" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>T_SEED_185</t>
+          <t>T_DB_5</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>5865.99</v>
+        <v>4500</v>
       </c>
       <c r="D186" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E186" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>T_SEED_186</t>
+          <t>T_DB_6</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>0</v>
       </c>
       <c r="C187" t="n">
-        <v>5577.33</v>
+        <v>2100</v>
       </c>
       <c r="D187" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>T_SEED_187</t>
+          <t>T_DB_7</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>0</v>
       </c>
       <c r="C188" t="n">
-        <v>2228.32</v>
+        <v>2100</v>
       </c>
       <c r="D188" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E188" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>T_SEED_188</t>
+          <t>T_DB_8</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>0</v>
       </c>
       <c r="C189" t="n">
-        <v>9025.59</v>
+        <v>2100</v>
       </c>
       <c r="D189" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>T_SEED_189</t>
+          <t>T_DB_9</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>0</v>
       </c>
       <c r="C190" t="n">
-        <v>7301.74</v>
+        <v>2100</v>
       </c>
       <c r="D190" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>T_SEED_190</t>
+          <t>T_DB_10</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>0</v>
       </c>
       <c r="C191" t="n">
-        <v>2363.07</v>
+        <v>2100</v>
       </c>
       <c r="D191" t="n">
         <v>2026</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>T_SEED_191</t>
+          <t>T_DB_11</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C192" t="n">
-        <v>2196.17</v>
+        <v>2100</v>
       </c>
       <c r="D192" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E192" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>T_SEED_192</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>1</v>
-      </c>
-      <c r="C193" t="n">
-        <v>9892.92</v>
-      </c>
-      <c r="D193" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E193" t="n">
-        <v>1</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2</v>
-      </c>
-      <c r="G193" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>T_SEED_193</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
-      <c r="C194" t="n">
-        <v>2447.35</v>
-      </c>
-      <c r="D194" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1</v>
-      </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>T_SEED_194</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>0</v>
-      </c>
-      <c r="C195" t="n">
-        <v>7491.09</v>
-      </c>
-      <c r="D195" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1</v>
-      </c>
-      <c r="F195" t="n">
-        <v>0</v>
-      </c>
-      <c r="G195" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>T_SEED_195</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
-      <c r="C196" t="n">
-        <v>4503.53</v>
-      </c>
-      <c r="D196" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="F196" t="n">
-        <v>3</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>T_SEED_196</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
-      <c r="C197" t="n">
-        <v>8338.52</v>
-      </c>
-      <c r="D197" t="n">
-        <v>2026</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>T_SEED_197</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>0</v>
-      </c>
-      <c r="C198" t="n">
-        <v>4389.41</v>
-      </c>
-      <c r="D198" t="n">
-        <v>2025</v>
-      </c>
-      <c r="E198" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>T_SEED_198</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>0</v>
-      </c>
-      <c r="C199" t="n">
-        <v>9758.200000000001</v>
-      </c>
-      <c r="D199" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2</v>
-      </c>
-      <c r="G199" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>T_SEED_199</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>1</v>
-      </c>
-      <c r="C200" t="n">
-        <v>8098.62</v>
-      </c>
-      <c r="D200" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E200" t="n">
-        <v>1</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>T_SEED_200</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
-      <c r="C201" t="n">
-        <v>7139.04</v>
-      </c>
-      <c r="D201" t="n">
-        <v>2024</v>
-      </c>
-      <c r="E201" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-      <c r="G201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
